--- a/data/sars/atlantic/tables/Atlantic_1998_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_1998_Table1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E68534-D204-9140-98E3-1448FD68E069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A51BBE-E9CA-8C42-A17C-623F4BA18668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="23700" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="54">
   <si>
     <t>Harbor seal</t>
   </si>
@@ -140,56 +140,6 @@
   </si>
   <si>
     <t>Blue whale</t>
-  </si>
-  <si>
-    <r>
-      <t>1,617</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>8,794</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Western</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> North Atlantic, coastal</t>
-    </r>
   </si>
   <si>
     <r>
@@ -219,20 +169,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>4,968</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
     <t>species</t>
   </si>
   <si>
@@ -266,7 +202,10 @@
     <t>strategic_yn</t>
   </si>
   <si>
-    <t>updated_yn</t>
+    <t>Western North Atlantic, coastal</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
   </si>
 </sst>
 </file>
@@ -277,7 +216,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -297,12 +236,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -334,54 +267,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,8 +626,8 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="47.3984375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="38" style="6" customWidth="1"/>
     <col min="3" max="3" width="8.19921875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="8" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.796875" style="6" bestFit="1" customWidth="1"/>
@@ -707,40 +643,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="M1" s="5"/>
     </row>
@@ -900,7 +836,7 @@
       </c>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
@@ -978,8 +914,8 @@
       </c>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.15">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A8" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -1018,7 +954,7 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.15">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -1095,8 +1031,8 @@
       </c>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="16" x14ac:dyDescent="0.15">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -1108,8 +1044,8 @@
       <c r="D11" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>40</v>
+      <c r="E11" s="15">
+        <v>1617</v>
       </c>
       <c r="F11" s="9">
         <v>0.04</v>
@@ -1134,7 +1070,7 @@
       </c>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
@@ -1147,8 +1083,8 @@
       <c r="D12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>40</v>
+      <c r="E12" s="15">
+        <v>1617</v>
       </c>
       <c r="F12" s="9">
         <v>0.04</v>
@@ -1251,7 +1187,7 @@
       </c>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="7" t="s">
         <v>21</v>
       </c>
@@ -1264,8 +1200,8 @@
       <c r="D15" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>41</v>
+      <c r="E15" s="15">
+        <v>8794</v>
       </c>
       <c r="F15" s="9">
         <v>0.04</v>
@@ -1289,12 +1225,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="31" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
@@ -1328,7 +1264,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.15">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -1366,7 +1302,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.15">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -1442,7 +1378,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.15">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="7" t="s">
@@ -1479,7 +1415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="7" t="s">
         <v>28</v>
       </c>
@@ -1518,7 +1454,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="15" x14ac:dyDescent="0.15">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="7" t="s">
@@ -1555,8 +1491,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.15">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A23" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -1593,9 +1529,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.15">
-      <c r="A24" s="5" t="s">
-        <v>43</v>
+    <row r="24" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A24" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>1</v>
@@ -1606,8 +1542,8 @@
       <c r="D24" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>44</v>
+      <c r="E24" s="15">
+        <v>4968</v>
       </c>
       <c r="F24" s="9">
         <v>0.04</v>
@@ -1707,8 +1643,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.15">
-      <c r="A27" s="13" t="s">
+    <row r="27" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+      <c r="A27" s="7" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="7" t="s">
@@ -1723,7 +1659,7 @@
       <c r="E27" s="11">
         <v>295</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="G27" s="12">
@@ -1735,7 +1671,7 @@
       <c r="I27" s="12">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>1.01</v>
       </c>
       <c r="K27" s="7" t="s">
@@ -1761,7 +1697,7 @@
       <c r="E28" s="8">
         <v>10019</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G28" s="12">
@@ -1773,7 +1709,7 @@
       <c r="I28" s="12">
         <v>5.7</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <v>4.4109999999999996</v>
       </c>
       <c r="K28" s="7" t="s">
@@ -1863,7 +1799,7 @@
       <c r="A31" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="16" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -1896,7 +1832,7 @@
       <c r="L31" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="M31" s="15"/>
+      <c r="M31" s="14"/>
     </row>
     <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
